--- a/backend/public/importaciones/plantilla_actualizacion_analisis.xlsx
+++ b/backend/public/importaciones/plantilla_actualizacion_analisis.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="300">
   <si>
     <t>cedula</t>
   </si>
@@ -150,15 +150,12 @@
     <t>1-0234-5678</t>
   </si>
   <si>
-    <t>ANA-84ABED55</t>
+    <t>26-00001-101-OP</t>
   </si>
   <si>
     <t>Juan</t>
   </si>
   <si>
-    <t>26-00001-101-OP</t>
-  </si>
-  <si>
     <t>Docente</t>
   </si>
   <si>
@@ -177,15 +174,12 @@
     <t>CRC</t>
   </si>
   <si>
-    <t>ANA-88A67106</t>
+    <t>26-00002-101-OP</t>
   </si>
   <si>
     <t>Maynor Toruño Pérez</t>
   </si>
   <si>
-    <t>26-00002-101-OP</t>
-  </si>
-  <si>
     <t>POLICIA</t>
   </si>
   <si>
@@ -201,243 +195,177 @@
     <t>APROBADO</t>
   </si>
   <si>
-    <t>ANA-FBC384C8</t>
+    <t>26-00003-101-OP</t>
   </si>
   <si>
     <t>Yeslin Xiomara Mora Castro</t>
   </si>
   <si>
-    <t>26-00003-101-OP</t>
-  </si>
-  <si>
     <t>ADMINISTRADORA</t>
   </si>
   <si>
     <t>HA SIDO BUENA CLIENTE</t>
   </si>
   <si>
-    <t>ANA-43C7D0AF</t>
+    <t>26-00004-101-OP</t>
   </si>
   <si>
     <t>Yader Samuel Jarquin Sossa</t>
   </si>
   <si>
-    <t>26-00004-101-OP</t>
-  </si>
-  <si>
     <t>RÉCORD CREDITICIO LIMPIO</t>
   </si>
   <si>
-    <t>ANA-881DBCDC</t>
+    <t>26-00005-101-OP</t>
   </si>
   <si>
     <t>Erick  Eduardo Mata Barrientos</t>
   </si>
   <si>
-    <t>26-00005-101-OP</t>
-  </si>
-  <si>
     <t>ADMINISTRADOR</t>
   </si>
   <si>
-    <t>ANA-D1497F65</t>
+    <t>26-00006-101-OP</t>
   </si>
   <si>
     <t>Jessie Gerardo Cruz Guido</t>
   </si>
   <si>
-    <t>26-00006-101-OP</t>
-  </si>
-  <si>
     <t>INTERINO</t>
   </si>
   <si>
     <t>BUEN RÉCORD CREDITICIO</t>
   </si>
   <si>
-    <t>ANA-55B4E06B</t>
+    <t>26-00007-101-OP</t>
   </si>
   <si>
     <t>Nogui Fainier Mena Delgado</t>
   </si>
   <si>
-    <t>26-00007-101-OP</t>
-  </si>
-  <si>
     <t>HA SIDO BUEN CLIENTE</t>
   </si>
   <si>
-    <t>ANA-4255FE8C</t>
+    <t>26-00008-101-OP</t>
   </si>
   <si>
     <t>Kattia María García Benavides</t>
   </si>
   <si>
-    <t>26-00008-101-OP</t>
-  </si>
-  <si>
     <t>DOCENTE</t>
   </si>
   <si>
     <t>INTERINA</t>
   </si>
   <si>
-    <t>ANA-B831E52A</t>
+    <t>26-00009-101-OP</t>
   </si>
   <si>
     <t>Diego Alejandro Zuñiga Mora</t>
   </si>
   <si>
-    <t>26-00009-101-OP</t>
-  </si>
-  <si>
     <t>BUEN RECORD CREDITICIO</t>
   </si>
   <si>
-    <t>ANA-08E4324A</t>
+    <t>26-00010-101-OP</t>
   </si>
   <si>
     <t>Donald Josué Goméz Moreno</t>
   </si>
   <si>
-    <t>26-00010-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-96131AF4</t>
+    <t>26-00011-101-OP</t>
   </si>
   <si>
     <t>Estefanny Orozco Maroto</t>
   </si>
   <si>
-    <t>26-00011-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-8E31F0E5</t>
+    <t>26-00012-101-OP</t>
   </si>
   <si>
     <t>María Chaves Hernánez</t>
   </si>
   <si>
-    <t>26-00012-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-7491296E</t>
+    <t>26-00013-101-OP</t>
   </si>
   <si>
     <t>Jennyfer Rebeca Gútierrez Chaves</t>
   </si>
   <si>
-    <t>26-00013-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-63FD8DCC</t>
+    <t>26-00014-101-OP</t>
   </si>
   <si>
     <t>Jefry Vital Rodríguez Alvarado</t>
   </si>
   <si>
-    <t>26-00014-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-C663D395</t>
+    <t>26-00015-101-OP</t>
   </si>
   <si>
     <t>Laura Johhana Lizano Jiménez</t>
   </si>
   <si>
-    <t>26-00015-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-E56E2A6D</t>
+    <t>26-00016-101-OP</t>
   </si>
   <si>
     <t>Cristian Menocal Cano</t>
   </si>
   <si>
-    <t>26-00016-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-7B82D3F5</t>
+    <t>26-00017-101-OP</t>
   </si>
   <si>
     <t>Diana Pricsilla Morena Fernandéz</t>
   </si>
   <si>
-    <t>26-00017-101-OP</t>
-  </si>
-  <si>
     <t>OFICINISTA</t>
   </si>
   <si>
-    <t>ANA-FB31DC2F</t>
+    <t>26-00018-101-OP</t>
   </si>
   <si>
     <t>José Reinaldo Meneses Rodriguéz</t>
   </si>
   <si>
-    <t>26-00018-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-F54A0C7D</t>
+    <t>26-00019-101-OP</t>
   </si>
   <si>
     <t>Andrea Esquivel Monge</t>
   </si>
   <si>
-    <t>26-00019-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-B1F9DA9F</t>
+    <t>26-00020-101-OP</t>
   </si>
   <si>
     <t>Luis Miguel Abarca Solis</t>
   </si>
   <si>
-    <t>26-00020-101-OP</t>
-  </si>
-  <si>
     <t>BUEN PEFFIL</t>
   </si>
   <si>
-    <t>ANA-9984C865</t>
+    <t>26-00021-101-OP</t>
   </si>
   <si>
     <t>Luis Emilio Arguedas Venegas</t>
   </si>
   <si>
-    <t>26-00021-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-382E28F0</t>
+    <t>26-00022-101-OP</t>
   </si>
   <si>
     <t>Elia Isabela Mejía Mata</t>
   </si>
   <si>
-    <t>26-00022-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-739FB737</t>
+    <t>26-00023-101-OP</t>
   </si>
   <si>
     <t>Harold Córdoba Sánchez</t>
   </si>
   <si>
-    <t>26-00023-101-OP</t>
-  </si>
-  <si>
     <t>BUEN PERFIL</t>
   </si>
   <si>
-    <t>ANA-B4515327</t>
+    <t>26-00024-101-OP</t>
   </si>
   <si>
     <t>Siney Villalobos Chacón</t>
   </si>
   <si>
-    <t>26-00024-101-OP</t>
-  </si>
-  <si>
     <t>Interino</t>
   </si>
   <si>
@@ -450,15 +378,12 @@
     <t>Aprobado</t>
   </si>
   <si>
-    <t>ANA-83DE997D</t>
+    <t>26-00025-101-OP</t>
   </si>
   <si>
     <t>Alonso Martinez Tames</t>
   </si>
   <si>
-    <t>26-00025-101-OP</t>
-  </si>
-  <si>
     <t>Policia</t>
   </si>
   <si>
@@ -468,45 +393,36 @@
     <t>Cliente con buena capacidad de pago</t>
   </si>
   <si>
-    <t>ANA-3C859E18</t>
+    <t>26-00026-101-OP</t>
   </si>
   <si>
     <t>Brayan Gaspar González</t>
   </si>
   <si>
-    <t>26-00026-101-OP</t>
-  </si>
-  <si>
     <t>Se aprueba crédito por buen comportamiento crediticio</t>
   </si>
   <si>
     <t>Historial crediticio positivo, sin atrasos relevantes.</t>
   </si>
   <si>
-    <t>ANA-276FA02D</t>
+    <t>26-00027-101-OP</t>
   </si>
   <si>
     <t>Yazmín Vallejos Vallejo</t>
   </si>
   <si>
-    <t>26-00027-101-OP</t>
-  </si>
-  <si>
     <t>Se aprueba crédito por estabilidad laboral</t>
   </si>
   <si>
     <t>Solicitante con empleo estable y continuidad comprobada.</t>
   </si>
   <si>
-    <t>ANA-E02F91B2</t>
+    <t>26-00028-101-OP</t>
   </si>
   <si>
     <t>Gilberto Mora Valverde</t>
   </si>
   <si>
-    <t>26-00028-101-OP</t>
-  </si>
-  <si>
     <t>Seguridad</t>
   </si>
   <si>
@@ -519,78 +435,60 @@
     <t>Solicitante de nuevo ingreso con buen perfil y adecuada capacidad de pago.</t>
   </si>
   <si>
-    <t>ANA-8DF5795E</t>
+    <t>26-00029-101-OP</t>
   </si>
   <si>
     <t>Adriana Chavarría Contreras</t>
   </si>
   <si>
-    <t>26-00029-101-OP</t>
-  </si>
-  <si>
     <t>Técnico</t>
   </si>
   <si>
-    <t>ANA-3AC3E43B</t>
+    <t>26-00030-101-OP</t>
   </si>
   <si>
     <t>Jazmín Rodríguiz Alfaro</t>
   </si>
   <si>
-    <t>26-00030-101-OP</t>
-  </si>
-  <si>
     <t>Se aprueba crédito por continuidad como cliente</t>
   </si>
   <si>
     <t>Relación comercial estable y sostenida en el tiempo</t>
   </si>
   <si>
-    <t>ANA-26A3E50A</t>
+    <t>26-00031-101-OP</t>
   </si>
   <si>
     <t>Orlando Cornejo Hernández</t>
   </si>
   <si>
-    <t>26-00031-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-5465674C</t>
+    <t>26-00032-101-OP</t>
   </si>
   <si>
     <t>Kensy Cruz Chaves</t>
   </si>
   <si>
-    <t>26-00032-101-OP</t>
-  </si>
-  <si>
     <t>Juez</t>
   </si>
   <si>
-    <t>ANA-1ED08E07</t>
+    <t>26-00033-101-OP</t>
   </si>
   <si>
     <t>Hazel Salas Gutiérrez</t>
   </si>
   <si>
-    <t>26-00033-101-OP</t>
-  </si>
-  <si>
     <t>Se aprueba crédito por ingresos comprobables</t>
   </si>
   <si>
     <t>Ingresos estables y debidamente verificados.</t>
   </si>
   <si>
-    <t>ANA-7AE0566E</t>
+    <t>26-00034-101-OP</t>
   </si>
   <si>
     <t>Brady Núñez Muños</t>
   </si>
   <si>
-    <t>26-00034-101-OP</t>
-  </si>
-  <si>
     <t>Investigador</t>
   </si>
   <si>
@@ -600,73 +498,55 @@
     <t>Perfil equilibrado entre ingresos, gastos y nivel de endeudamiento</t>
   </si>
   <si>
-    <t>ANA-94436F90</t>
+    <t>26-00035-101-OP</t>
   </si>
   <si>
     <t>Verónica Mena Castro</t>
   </si>
   <si>
-    <t>26-00035-101-OP</t>
-  </si>
-  <si>
     <t>Profesional de ingresos</t>
   </si>
   <si>
-    <t>ANA-52C23F1A</t>
+    <t>26-00036-101-OP</t>
   </si>
   <si>
     <t>Roldán Baltodano Baltodano</t>
   </si>
   <si>
-    <t>26-00036-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-406294DF</t>
+    <t>26-00037-101-OP</t>
   </si>
   <si>
     <t>Julietha Fallas Valverde</t>
   </si>
   <si>
-    <t>26-00037-101-OP</t>
-  </si>
-  <si>
     <t>Profesional</t>
   </si>
   <si>
     <t>Ingresos suficientes para asumir la obligación sin dificultad.</t>
   </si>
   <si>
-    <t>ANA-2ACDBD11</t>
+    <t>26-00038-101-OP</t>
   </si>
   <si>
     <t>Carlos Umaña Hidalgo</t>
   </si>
   <si>
-    <t>26-00038-101-OP</t>
-  </si>
-  <si>
     <t>Se aprueba crédito por respaldo económico</t>
   </si>
   <si>
     <t>Solicitante cuenta con soporte financiero suficiente.</t>
   </si>
   <si>
-    <t>ANA-CDA45111</t>
+    <t>26-00039-101-OP</t>
   </si>
   <si>
     <t>Óscar Portillo Alvarado</t>
   </si>
   <si>
-    <t>26-00039-101-OP</t>
-  </si>
-  <si>
-    <t>ANA-F7EE6FD6</t>
+    <t>26-00040-101-OP</t>
   </si>
   <si>
     <t>Roger Requenes Trejos</t>
-  </si>
-  <si>
-    <t>26-00040-101-OP</t>
   </si>
   <si>
     <t>Pensionado</t>
@@ -1754,13 +1634,13 @@
         <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="G2" s="4">
         <v>800000.0</v>
@@ -1811,17 +1691,17 @@
         <v>36</v>
       </c>
       <c r="AI2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AK2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="AK2" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="AL2" s="4"/>
       <c r="AM2" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN2" s="4">
         <v>0</v>
@@ -1838,19 +1718,19 @@
         <v>502860669</v>
       </c>
       <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
       </c>
       <c r="G3">
         <v>836398.0</v>
@@ -1883,16 +1763,16 @@
         <v>18</v>
       </c>
       <c r="AI3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK3" t="s">
         <v>57</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>59</v>
-      </c>
       <c r="AM3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN3">
         <v>5</v>
@@ -1909,19 +1789,19 @@
         <v>111790550</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="F4" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G4" s="4">
         <v>1433828.0</v>
@@ -1972,17 +1852,17 @@
         <v>18</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AJ4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK4" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AK4" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN4" s="4">
         <v>10</v>
@@ -1999,19 +1879,19 @@
         <v>116190424</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>70297150.0</v>
@@ -2044,16 +1924,16 @@
         <v>18</v>
       </c>
       <c r="AI5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK5" t="s">
         <v>57</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>59</v>
-      </c>
       <c r="AM5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN5">
         <v>2</v>
@@ -2070,19 +1950,19 @@
         <v>114490480</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G6" s="4">
         <v>576597.0</v>
@@ -2133,17 +2013,17 @@
         <v>18</v>
       </c>
       <c r="AI6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK6" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AJ6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK6" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL6" s="4"/>
       <c r="AM6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN6" s="4">
         <v>3</v>
@@ -2160,19 +2040,19 @@
         <v>115360714</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>590006.0</v>
@@ -2205,16 +2085,16 @@
         <v>18</v>
       </c>
       <c r="AI7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK7" t="s">
         <v>57</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>59</v>
-      </c>
       <c r="AM7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -2231,19 +2111,19 @@
         <v>603650141</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8" s="4">
         <v>819818.0</v>
@@ -2294,17 +2174,17 @@
         <v>18</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN8" s="4">
         <v>1</v>
@@ -2321,19 +2201,19 @@
         <v>206060517</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G9">
         <v>1496586.0</v>
@@ -2366,16 +2246,16 @@
         <v>18</v>
       </c>
       <c r="AI9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK9" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>59</v>
-      </c>
       <c r="AM9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN9">
         <v>8</v>
@@ -2392,19 +2272,19 @@
         <v>109450959</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G10" s="4">
         <v>780957.0</v>
@@ -2455,17 +2335,17 @@
         <v>12</v>
       </c>
       <c r="AI10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK10" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AJ10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK10" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN10" s="4">
         <v>0</v>
@@ -2482,19 +2362,19 @@
         <v>603650739</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>1689790.0</v>
@@ -2527,16 +2407,16 @@
         <v>24</v>
       </c>
       <c r="AI11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK11" t="s">
         <v>57</v>
       </c>
-      <c r="AK11" t="s">
-        <v>59</v>
-      </c>
       <c r="AM11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN11">
         <v>2</v>
@@ -2553,19 +2433,19 @@
         <v>304330713</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G12" s="4">
         <v>1598450.0</v>
@@ -2616,17 +2496,17 @@
         <v>18</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK12" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AK12" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN12" s="4">
         <v>3</v>
@@ -2643,19 +2523,19 @@
         <v>401670693</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>1462531.0</v>
@@ -2688,16 +2568,16 @@
         <v>18</v>
       </c>
       <c r="AI13" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="s">
         <v>57</v>
       </c>
-      <c r="AK13" t="s">
-        <v>59</v>
-      </c>
       <c r="AM13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN13">
         <v>8</v>
@@ -2714,19 +2594,19 @@
         <v>109620629</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4">
         <v>978776.0</v>
@@ -2777,17 +2657,17 @@
         <v>12</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK14" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AK14" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN14" s="4">
         <v>2</v>
@@ -2804,19 +2684,19 @@
         <v>207140520</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>726982.0</v>
@@ -2849,16 +2729,16 @@
         <v>24</v>
       </c>
       <c r="AI15" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK15" t="s">
         <v>57</v>
       </c>
-      <c r="AK15" t="s">
-        <v>59</v>
-      </c>
       <c r="AM15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN15">
         <v>3</v>
@@ -2875,19 +2755,19 @@
         <v>114360270</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G16" s="4">
         <v>561741.0</v>
@@ -2938,17 +2818,17 @@
         <v>12</v>
       </c>
       <c r="AI16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK16" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AJ16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK16" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN16" s="4">
         <v>11</v>
@@ -2965,19 +2845,19 @@
         <v>503720670</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>780957.0</v>
@@ -3010,16 +2890,16 @@
         <v>18</v>
       </c>
       <c r="AI17" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="s">
         <v>57</v>
       </c>
-      <c r="AK17" t="s">
-        <v>59</v>
-      </c>
       <c r="AM17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN17">
         <v>14</v>
@@ -3036,19 +2916,19 @@
         <v>114670582</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G18" s="4">
         <v>786157.0</v>
@@ -3099,17 +2979,17 @@
         <v>24</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK18" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AK18" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN18" s="4">
         <v>1</v>
@@ -3126,19 +3006,19 @@
         <v>113430288</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G19">
         <v>780957.0</v>
@@ -3171,16 +3051,16 @@
         <v>24</v>
       </c>
       <c r="AI19" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK19" t="s">
         <v>57</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>59</v>
-      </c>
       <c r="AM19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN19">
         <v>0</v>
@@ -3197,19 +3077,19 @@
         <v>205830470</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G20" s="4">
         <v>1164671.0</v>
@@ -3260,17 +3140,17 @@
         <v>18</v>
       </c>
       <c r="AI20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK20" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AJ20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK20" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN20" s="4">
         <v>1</v>
@@ -3287,19 +3167,19 @@
         <v>304200783</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G21">
         <v>1606865.0</v>
@@ -3332,16 +3212,16 @@
         <v>24</v>
       </c>
       <c r="AI21" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>105</v>
+      </c>
+      <c r="AK21" t="s">
         <v>57</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>59</v>
-      </c>
       <c r="AM21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN21">
         <v>11</v>
@@ -3358,19 +3238,19 @@
         <v>109310986</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G22" s="4">
         <v>892605.0</v>
@@ -3421,17 +3301,17 @@
         <v>24</v>
       </c>
       <c r="AI22" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AJ22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK22" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AK22" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN22" s="4">
         <v>10</v>
@@ -3448,19 +3328,19 @@
         <v>109210445</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G23">
         <v>634813.0</v>
@@ -3493,16 +3373,16 @@
         <v>24</v>
       </c>
       <c r="AI23" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AJ23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK23" t="s">
         <v>57</v>
       </c>
-      <c r="AK23" t="s">
-        <v>59</v>
-      </c>
       <c r="AM23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN23">
         <v>0</v>
@@ -3519,19 +3399,19 @@
         <v>107000907</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G24" s="4">
         <v>672636.0</v>
@@ -3582,17 +3462,17 @@
         <v>24</v>
       </c>
       <c r="AI24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK24" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="AJ24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK24" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN24" s="4">
         <v>4</v>
@@ -3609,19 +3489,19 @@
         <v>603850364</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G25">
         <v>1083643.0</v>
@@ -3654,16 +3534,16 @@
         <v>18</v>
       </c>
       <c r="AI25" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="AJ25" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="AK25" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN25">
         <v>15</v>
@@ -3680,19 +3560,19 @@
         <v>304470608</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G26" s="4">
         <v>748.99000000000001</v>
@@ -3743,17 +3623,17 @@
         <v>18</v>
       </c>
       <c r="AI26" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="AJ26" s="4" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="AK26" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL26" s="4"/>
       <c r="AM26" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN26" s="4">
         <v>12</v>
@@ -3770,19 +3650,19 @@
         <v>112990034</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G27">
         <v>745971.0</v>
@@ -3815,16 +3695,16 @@
         <v>24</v>
       </c>
       <c r="AI27" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="AJ27" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="AK27" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN27">
         <v>4</v>
@@ -3841,19 +3721,19 @@
         <v>114650007</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G28" s="4">
         <v>703920.0</v>
@@ -3904,17 +3784,17 @@
         <v>18</v>
       </c>
       <c r="AI28" s="4" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="AJ28" s="4" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="AK28" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL28" s="4"/>
       <c r="AM28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN28" s="4">
         <v>4</v>
@@ -3931,19 +3811,19 @@
         <v>700830074</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G29">
         <v>512892.0</v>
@@ -3976,16 +3856,16 @@
         <v>18</v>
       </c>
       <c r="AI29" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="AJ29" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN29">
         <v>7</v>
@@ -4002,19 +3882,19 @@
         <v>113020495</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G30" s="4">
         <v>554319.0</v>
@@ -4065,17 +3945,17 @@
         <v>24</v>
       </c>
       <c r="AI30" s="4" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="AJ30" s="4" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="AK30" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL30" s="4"/>
       <c r="AM30" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN30" s="4">
         <v>8</v>
@@ -4092,19 +3972,19 @@
         <v>304190667</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G31">
         <v>1319863.0</v>
@@ -4137,16 +4017,16 @@
         <v>18</v>
       </c>
       <c r="AI31" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="AJ31" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="AK31" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN31">
         <v>14</v>
@@ -4163,19 +4043,19 @@
         <v>111490443</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G32" s="4">
         <v>848801.0</v>
@@ -4226,17 +4106,17 @@
         <v>18</v>
       </c>
       <c r="AI32" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="AJ32" s="4" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="AK32" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL32" s="4"/>
       <c r="AM32" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN32" s="4">
         <v>6</v>
@@ -4253,19 +4133,19 @@
         <v>603710486</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="F33" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G33">
         <v>3359433.0</v>
@@ -4298,16 +4178,16 @@
         <v>36</v>
       </c>
       <c r="AI33" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="AJ33" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="AK33" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN33">
         <v>3</v>
@@ -4324,19 +4204,19 @@
         <v>304810776</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G34" s="4">
         <v>692277.0</v>
@@ -4387,17 +4267,17 @@
         <v>24</v>
       </c>
       <c r="AI34" s="4" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="AJ34" s="4" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="AK34" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL34" s="4"/>
       <c r="AM34" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN34" s="4">
         <v>3</v>
@@ -4414,19 +4294,19 @@
         <v>117690229</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="F35" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G35">
         <v>953966.0</v>
@@ -4459,16 +4339,16 @@
         <v>18</v>
       </c>
       <c r="AI35" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="AJ35" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="AK35" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN35">
         <v>20</v>
@@ -4485,19 +4365,19 @@
         <v>112360004</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G36" s="4">
         <v>1039958.0</v>
@@ -4548,17 +4428,17 @@
         <v>48</v>
       </c>
       <c r="AI36" s="4" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="AJ36" s="4" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="AK36" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL36" s="4"/>
       <c r="AM36" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN36" s="4">
         <v>6</v>
@@ -4575,19 +4455,19 @@
         <v>206140307</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="F37" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G37">
         <v>705442.0</v>
@@ -4620,16 +4500,16 @@
         <v>24</v>
       </c>
       <c r="AI37" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="AJ37" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="AK37" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN37">
         <v>0</v>
@@ -4646,19 +4526,19 @@
         <v>108620044</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G38" s="4">
         <v>1323149.0</v>
@@ -4709,17 +4589,17 @@
         <v>24</v>
       </c>
       <c r="AI38" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="AJ38" s="4" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="AK38" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL38" s="4"/>
       <c r="AM38" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN38" s="4">
         <v>1</v>
@@ -4736,19 +4616,19 @@
         <v>702170669</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="E39" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F39" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G39">
         <v>735287.0</v>
@@ -4781,16 +4661,16 @@
         <v>24</v>
       </c>
       <c r="AI39" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="AJ39" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="AK39" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN39">
         <v>5</v>
@@ -4807,19 +4687,19 @@
         <v>113340607</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G40" s="4">
         <v>856371.0</v>
@@ -4870,17 +4750,17 @@
         <v>18</v>
       </c>
       <c r="AI40" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="AJ40" s="4" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="AK40" s="4" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AL40" s="4"/>
       <c r="AM40" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN40" s="4">
         <v>2</v>
@@ -4897,19 +4777,19 @@
         <v>601600188</v>
       </c>
       <c r="B41" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="E41" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="F41" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G41">
         <v>1617256.0</v>
@@ -4942,16 +4822,16 @@
         <v>18</v>
       </c>
       <c r="AI41" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="AJ41" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="AK41" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AM41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN41">
         <v>0</v>
@@ -4991,19 +4871,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5011,7 +4891,7 @@
         <v>502860669</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -5023,7 +4903,7 @@
         <v>502860669</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -5035,7 +4915,7 @@
         <v>502860669</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -5047,7 +4927,7 @@
         <v>502860669</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -5059,7 +4939,7 @@
         <v>502860669</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -5071,7 +4951,7 @@
         <v>111790550</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -5083,7 +4963,7 @@
         <v>111790550</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -5095,7 +4975,7 @@
         <v>111790550</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -5107,7 +4987,7 @@
         <v>111790550</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -5119,7 +4999,7 @@
         <v>111790550</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -5131,7 +5011,7 @@
         <v>111790550</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -5143,7 +5023,7 @@
         <v>111790550</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -5155,7 +5035,7 @@
         <v>111790550</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -5167,7 +5047,7 @@
         <v>111790550</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -5179,7 +5059,7 @@
         <v>111790550</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -5191,7 +5071,7 @@
         <v>116190424</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -5203,7 +5083,7 @@
         <v>116190424</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -5215,7 +5095,7 @@
         <v>114490480</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -5227,7 +5107,7 @@
         <v>114490480</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -5239,7 +5119,7 @@
         <v>114490480</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -5251,7 +5131,7 @@
         <v>115360714</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -5263,7 +5143,7 @@
         <v>603650141</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -5275,7 +5155,7 @@
         <v>206060517</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -5287,7 +5167,7 @@
         <v>206060517</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -5299,7 +5179,7 @@
         <v>206060517</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -5311,7 +5191,7 @@
         <v>206060517</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -5323,7 +5203,7 @@
         <v>206060517</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -5335,7 +5215,7 @@
         <v>206060517</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -5347,7 +5227,7 @@
         <v>206060517</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -5359,7 +5239,7 @@
         <v>206060517</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -5371,7 +5251,7 @@
         <v>603650739</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -5383,7 +5263,7 @@
         <v>603650739</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -5395,7 +5275,7 @@
         <v>304330713</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -5407,7 +5287,7 @@
         <v>304330713</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -5419,7 +5299,7 @@
         <v>304330713</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -5431,7 +5311,7 @@
         <v>401670693</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -5443,7 +5323,7 @@
         <v>401670693</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -5455,7 +5335,7 @@
         <v>401670693</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -5467,7 +5347,7 @@
         <v>401670693</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -5479,7 +5359,7 @@
         <v>401670693</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -5491,7 +5371,7 @@
         <v>401670693</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -5503,7 +5383,7 @@
         <v>401670693</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -5515,7 +5395,7 @@
         <v>401670693</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -5527,7 +5407,7 @@
         <v>109620629</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -5539,7 +5419,7 @@
         <v>109620629</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -5551,7 +5431,7 @@
         <v>207140520</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -5563,7 +5443,7 @@
         <v>207140520</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -5575,7 +5455,7 @@
         <v>207140520</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -5587,7 +5467,7 @@
         <v>114360270</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -5599,7 +5479,7 @@
         <v>114360270</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -5611,7 +5491,7 @@
         <v>114360270</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -5623,7 +5503,7 @@
         <v>114360270</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -5635,7 +5515,7 @@
         <v>114360270</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -5647,7 +5527,7 @@
         <v>114360270</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -5659,7 +5539,7 @@
         <v>114360270</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -5671,7 +5551,7 @@
         <v>114360270</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -5683,7 +5563,7 @@
         <v>114360270</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -5695,7 +5575,7 @@
         <v>114360270</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -5707,7 +5587,7 @@
         <v>114360270</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -5719,7 +5599,7 @@
         <v>503720670</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -5731,7 +5611,7 @@
         <v>503720670</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -5743,7 +5623,7 @@
         <v>503720670</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -5755,7 +5635,7 @@
         <v>503720670</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -5767,7 +5647,7 @@
         <v>503720670</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -5779,7 +5659,7 @@
         <v>503720670</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -5791,7 +5671,7 @@
         <v>503720670</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -5803,7 +5683,7 @@
         <v>503720670</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -5815,7 +5695,7 @@
         <v>503720670</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -5827,7 +5707,7 @@
         <v>503720670</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -5839,7 +5719,7 @@
         <v>503720670</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -5851,7 +5731,7 @@
         <v>503720670</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -5863,7 +5743,7 @@
         <v>503720670</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -5875,7 +5755,7 @@
         <v>503720670</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -5887,7 +5767,7 @@
         <v>114670582</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -5899,7 +5779,7 @@
         <v>205830470</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -5911,7 +5791,7 @@
         <v>304200783</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -5923,7 +5803,7 @@
         <v>304200783</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -5935,7 +5815,7 @@
         <v>304200783</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -5947,7 +5827,7 @@
         <v>304200783</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -5959,7 +5839,7 @@
         <v>304200783</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -5971,7 +5851,7 @@
         <v>304200783</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -5983,7 +5863,7 @@
         <v>304200783</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -5995,7 +5875,7 @@
         <v>304200783</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -6007,7 +5887,7 @@
         <v>304200783</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
@@ -6019,7 +5899,7 @@
         <v>304200783</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -6031,7 +5911,7 @@
         <v>304200783</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -6043,7 +5923,7 @@
         <v>109310986</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
@@ -6055,7 +5935,7 @@
         <v>109310986</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -6067,7 +5947,7 @@
         <v>109310986</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -6079,7 +5959,7 @@
         <v>109310986</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -6091,7 +5971,7 @@
         <v>109310986</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -6103,7 +5983,7 @@
         <v>109310986</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -6115,7 +5995,7 @@
         <v>109310986</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -6127,7 +6007,7 @@
         <v>109310986</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -6139,7 +6019,7 @@
         <v>109310986</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -6151,7 +6031,7 @@
         <v>109310986</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -6163,7 +6043,7 @@
         <v>107000907</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
@@ -6175,7 +6055,7 @@
         <v>107000907</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -6187,7 +6067,7 @@
         <v>107000907</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
@@ -6199,7 +6079,7 @@
         <v>107000907</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
@@ -6211,7 +6091,7 @@
         <v>603850364</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
@@ -6223,7 +6103,7 @@
         <v>603850364</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
@@ -6235,7 +6115,7 @@
         <v>603850364</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
@@ -6247,7 +6127,7 @@
         <v>603850364</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
@@ -6259,7 +6139,7 @@
         <v>603850364</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -6271,7 +6151,7 @@
         <v>603850364</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -6283,7 +6163,7 @@
         <v>603850364</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
@@ -6295,7 +6175,7 @@
         <v>603850364</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
@@ -6307,7 +6187,7 @@
         <v>603850364</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
@@ -6319,7 +6199,7 @@
         <v>603850364</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
@@ -6331,7 +6211,7 @@
         <v>603850364</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
@@ -6343,7 +6223,7 @@
         <v>603850364</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -6355,7 +6235,7 @@
         <v>603850364</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -6367,7 +6247,7 @@
         <v>603850364</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
@@ -6379,7 +6259,7 @@
         <v>603850364</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
@@ -6391,7 +6271,7 @@
         <v>304470608</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -6403,7 +6283,7 @@
         <v>304470608</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -6415,7 +6295,7 @@
         <v>304470608</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
@@ -6427,7 +6307,7 @@
         <v>304470608</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
@@ -6439,7 +6319,7 @@
         <v>304470608</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
@@ -6451,7 +6331,7 @@
         <v>304470608</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
@@ -6463,7 +6343,7 @@
         <v>304470608</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
@@ -6475,7 +6355,7 @@
         <v>304470608</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
@@ -6487,7 +6367,7 @@
         <v>304470608</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -6499,7 +6379,7 @@
         <v>304470608</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
@@ -6511,7 +6391,7 @@
         <v>304470608</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
@@ -6523,7 +6403,7 @@
         <v>304470608</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
@@ -6535,7 +6415,7 @@
         <v>112990034</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
@@ -6547,7 +6427,7 @@
         <v>112990034</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
@@ -6559,7 +6439,7 @@
         <v>112990034</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
@@ -6571,7 +6451,7 @@
         <v>112990034</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
@@ -6583,7 +6463,7 @@
         <v>114650007</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
@@ -6595,7 +6475,7 @@
         <v>114650007</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
@@ -6607,7 +6487,7 @@
         <v>114650007</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -6619,7 +6499,7 @@
         <v>114650007</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
@@ -6631,7 +6511,7 @@
         <v>700830074</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -6643,7 +6523,7 @@
         <v>700830074</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -6655,7 +6535,7 @@
         <v>700830074</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -6667,7 +6547,7 @@
         <v>700830074</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
@@ -6679,7 +6559,7 @@
         <v>700830074</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -6691,7 +6571,7 @@
         <v>700830074</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
@@ -6703,7 +6583,7 @@
         <v>700830074</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -6715,7 +6595,7 @@
         <v>113020495</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
@@ -6727,7 +6607,7 @@
         <v>113020495</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -6739,7 +6619,7 @@
         <v>113020495</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
@@ -6751,7 +6631,7 @@
         <v>113020495</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -6763,7 +6643,7 @@
         <v>113020495</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
@@ -6775,7 +6655,7 @@
         <v>113020495</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -6787,7 +6667,7 @@
         <v>113020495</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
@@ -6799,7 +6679,7 @@
         <v>113020495</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
@@ -6811,7 +6691,7 @@
         <v>304190667</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
@@ -6823,7 +6703,7 @@
         <v>304190667</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
@@ -6835,7 +6715,7 @@
         <v>304190667</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
@@ -6847,7 +6727,7 @@
         <v>304190667</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -6859,7 +6739,7 @@
         <v>304190667</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -6871,7 +6751,7 @@
         <v>304190667</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -6883,7 +6763,7 @@
         <v>304190667</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -6895,7 +6775,7 @@
         <v>304190667</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -6907,7 +6787,7 @@
         <v>304190667</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -6919,7 +6799,7 @@
         <v>304190667</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -6931,7 +6811,7 @@
         <v>304190667</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -6943,7 +6823,7 @@
         <v>304190667</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -6955,7 +6835,7 @@
         <v>304190667</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -6967,7 +6847,7 @@
         <v>304190667</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -6979,7 +6859,7 @@
         <v>111490443</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -6991,7 +6871,7 @@
         <v>111490443</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -7003,7 +6883,7 @@
         <v>111490443</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -7015,7 +6895,7 @@
         <v>111490443</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -7027,7 +6907,7 @@
         <v>111490443</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -7039,7 +6919,7 @@
         <v>111490443</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -7051,7 +6931,7 @@
         <v>603710486</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -7063,7 +6943,7 @@
         <v>603710486</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -7075,7 +6955,7 @@
         <v>603710486</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -7087,7 +6967,7 @@
         <v>304810776</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -7099,7 +6979,7 @@
         <v>304810776</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -7111,7 +6991,7 @@
         <v>304810776</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -7123,7 +7003,7 @@
         <v>117690229</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -7135,7 +7015,7 @@
         <v>117690229</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -7147,7 +7027,7 @@
         <v>117690229</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -7159,7 +7039,7 @@
         <v>117690229</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -7171,7 +7051,7 @@
         <v>117690229</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -7183,7 +7063,7 @@
         <v>117690229</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -7195,7 +7075,7 @@
         <v>117690229</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -7207,7 +7087,7 @@
         <v>117690229</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -7219,7 +7099,7 @@
         <v>117690229</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -7231,7 +7111,7 @@
         <v>117690229</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -7243,7 +7123,7 @@
         <v>117690229</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -7255,7 +7135,7 @@
         <v>117690229</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -7267,7 +7147,7 @@
         <v>117690229</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -7279,7 +7159,7 @@
         <v>117690229</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -7291,7 +7171,7 @@
         <v>117690229</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -7303,7 +7183,7 @@
         <v>117690229</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -7315,7 +7195,7 @@
         <v>117690229</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -7327,7 +7207,7 @@
         <v>117690229</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -7339,7 +7219,7 @@
         <v>117690229</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -7351,7 +7231,7 @@
         <v>117690229</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -7363,7 +7243,7 @@
         <v>112360004</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -7375,7 +7255,7 @@
         <v>112360004</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -7387,7 +7267,7 @@
         <v>112360004</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -7399,7 +7279,7 @@
         <v>112360004</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -7411,7 +7291,7 @@
         <v>112360004</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -7423,7 +7303,7 @@
         <v>112360004</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -7435,7 +7315,7 @@
         <v>108620044</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -7447,7 +7327,7 @@
         <v>702170669</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -7459,7 +7339,7 @@
         <v>702170669</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -7471,7 +7351,7 @@
         <v>702170669</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -7483,7 +7363,7 @@
         <v>702170669</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -7495,7 +7375,7 @@
         <v>702170669</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -7507,7 +7387,7 @@
         <v>113340607</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -7519,7 +7399,7 @@
         <v>113340607</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -7529,19 +7409,19 @@
     <row r="212" spans="1:6">
       <c r="A212" s="8"/>
       <c r="B212" s="8" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -7573,22 +7453,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7596,7 +7476,7 @@
         <v>502860669</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -7609,7 +7489,7 @@
         <v>111790550</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -7622,7 +7502,7 @@
         <v>114490480</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -7635,7 +7515,7 @@
         <v>114490480</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -7648,7 +7528,7 @@
         <v>114490480</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -7661,7 +7541,7 @@
         <v>114490480</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -7674,7 +7554,7 @@
         <v>115360714</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -7687,7 +7567,7 @@
         <v>603650141</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -7700,7 +7580,7 @@
         <v>206060517</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -7713,7 +7593,7 @@
         <v>206060517</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -7726,7 +7606,7 @@
         <v>109450959</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -7739,7 +7619,7 @@
         <v>603650739</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -7752,7 +7632,7 @@
         <v>603650739</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -7765,7 +7645,7 @@
         <v>603650739</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -7778,7 +7658,7 @@
         <v>603650739</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -7791,7 +7671,7 @@
         <v>304330713</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -7804,7 +7684,7 @@
         <v>304330713</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -7817,7 +7697,7 @@
         <v>304330713</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -7830,7 +7710,7 @@
         <v>304330713</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -7843,7 +7723,7 @@
         <v>401670693</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -7856,7 +7736,7 @@
         <v>401670693</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -7869,7 +7749,7 @@
         <v>109620629</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -7882,7 +7762,7 @@
         <v>109620629</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -7895,7 +7775,7 @@
         <v>109620629</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -7908,7 +7788,7 @@
         <v>109620629</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -7921,7 +7801,7 @@
         <v>109620629</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -7934,7 +7814,7 @@
         <v>114360270</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -7947,7 +7827,7 @@
         <v>114360270</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -7960,7 +7840,7 @@
         <v>114360270</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -7973,7 +7853,7 @@
         <v>114360270</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -7986,7 +7866,7 @@
         <v>114360270</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -7999,7 +7879,7 @@
         <v>503720670</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -8012,7 +7892,7 @@
         <v>503720670</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -8025,7 +7905,7 @@
         <v>205830470</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -8038,7 +7918,7 @@
         <v>304200783</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -8051,7 +7931,7 @@
         <v>304200783</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -8064,7 +7944,7 @@
         <v>109310986</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -8077,7 +7957,7 @@
         <v>107000907</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -8090,7 +7970,7 @@
         <v>107000907</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -8103,7 +7983,7 @@
         <v>107000907</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -8116,7 +7996,7 @@
         <v>107000907</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -8129,7 +8009,7 @@
         <v>603850364</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -8142,7 +8022,7 @@
         <v>603850364</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -8155,7 +8035,7 @@
         <v>603850364</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -8168,7 +8048,7 @@
         <v>304470608</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -8181,7 +8061,7 @@
         <v>112990034</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -8194,7 +8074,7 @@
         <v>112990034</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -8207,7 +8087,7 @@
         <v>112990034</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -8220,7 +8100,7 @@
         <v>112990034</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
@@ -8233,7 +8113,7 @@
         <v>113020495</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -8246,7 +8126,7 @@
         <v>113020495</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
@@ -8259,7 +8139,7 @@
         <v>304190667</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -8272,7 +8152,7 @@
         <v>304190667</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -8285,7 +8165,7 @@
         <v>304190667</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
@@ -8298,7 +8178,7 @@
         <v>304190667</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -8311,7 +8191,7 @@
         <v>111490443</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
@@ -8324,7 +8204,7 @@
         <v>111490443</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -8337,7 +8217,7 @@
         <v>111490443</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -8350,7 +8230,7 @@
         <v>111490443</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -8363,7 +8243,7 @@
         <v>304810776</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -8376,7 +8256,7 @@
         <v>112360004</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -8389,7 +8269,7 @@
         <v>112360004</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -8402,7 +8282,7 @@
         <v>206140307</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -8415,7 +8295,7 @@
         <v>108620044</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -8428,7 +8308,7 @@
         <v>108620044</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
@@ -8441,7 +8321,7 @@
         <v>108620044</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -8454,7 +8334,7 @@
         <v>108620044</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -8467,7 +8347,7 @@
         <v>108620044</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -8480,7 +8360,7 @@
         <v>113340607</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -8493,7 +8373,7 @@
         <v>113340607</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -8506,7 +8386,7 @@
         <v>601600188</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -8517,22 +8397,22 @@
     <row r="73" spans="1:7">
       <c r="A73" s="8"/>
       <c r="B73" s="8" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -8563,19 +8443,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8583,7 +8463,7 @@
         <v>502860669</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -8595,7 +8475,7 @@
         <v>114490480</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -8607,7 +8487,7 @@
         <v>115360714</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -8619,7 +8499,7 @@
         <v>603650141</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -8631,7 +8511,7 @@
         <v>109450959</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -8643,7 +8523,7 @@
         <v>603650739</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -8655,7 +8535,7 @@
         <v>304330713</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -8667,7 +8547,7 @@
         <v>109620629</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -8679,7 +8559,7 @@
         <v>114670582</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -8691,7 +8571,7 @@
         <v>113430288</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -8703,7 +8583,7 @@
         <v>205830470</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -8715,7 +8595,7 @@
         <v>304200783</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -8727,7 +8607,7 @@
         <v>107000907</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -8739,7 +8619,7 @@
         <v>113020495</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -8751,7 +8631,7 @@
         <v>111490443</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -8763,7 +8643,7 @@
         <v>108620044</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -8773,19 +8653,19 @@
     <row r="18" spans="1:6">
       <c r="A18" s="8"/>
       <c r="B18" s="8" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -8814,133 +8694,133 @@
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="28">
       <c r="A1" s="12" t="s">
-        <v>275</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:7" customHeight="1" ht="20">
       <c r="A3" s="14" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:7" customHeight="1" ht="32">
       <c r="A4" s="1" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:7" customHeight="1" ht="32">
       <c r="A5" s="1" t="s">
-        <v>279</v>
+        <v>239</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:7" customHeight="1" ht="32">
       <c r="A6" s="1" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="32">
       <c r="A7" s="1" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="32">
       <c r="A8" s="1" t="s">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="20">
       <c r="A10" s="14" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:7" customHeight="1" ht="25">
       <c r="A11" s="15" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="30">
       <c r="A13" s="16" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="30">
       <c r="A14" s="16" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="30">
       <c r="A15" s="16" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="20">
       <c r="A17" s="17" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="35">
       <c r="A18" s="1" t="s">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>297</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:7" customHeight="1" ht="35">
       <c r="A19" s="1" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="35">
       <c r="A20" s="1" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="35">
       <c r="A21" s="1" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>303</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="20">
       <c r="A23" s="18" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="19" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8948,19 +8828,19 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8968,14 +8848,14 @@
         <v>603850364</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="F26" s="20">
         <v>150000</v>
@@ -8986,16 +8866,16 @@
         <v>603850364</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="F27" s="20">
         <v>80000</v>
@@ -9003,12 +8883,12 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="21" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="19" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -9016,22 +8896,22 @@
         <v>0</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -9039,17 +8919,17 @@
         <v>304470608</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22" t="s">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>317</v>
+        <v>277</v>
       </c>
       <c r="G32" s="22">
         <v>500000</v>
@@ -9057,12 +8937,12 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="21" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="19" t="s">
-        <v>319</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -9073,7 +8953,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>4</v>
@@ -9093,10 +8973,10 @@
         <v>603850364</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4">
@@ -9106,28 +8986,28 @@
         <v>620000</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>321</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="21" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="1:7" customHeight="1" ht="20">
       <c r="A40" s="14" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="13" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>326</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -9135,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>327</v>
+        <v>287</v>
       </c>
       <c r="C42" s="15"/>
     </row>
@@ -9144,7 +9024,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>328</v>
+        <v>288</v>
       </c>
       <c r="C43" s="24"/>
     </row>
@@ -9153,7 +9033,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="C44" s="15"/>
     </row>
@@ -9162,54 +9042,54 @@
         <v>38</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="4" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
